--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_tous.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_tous.xlsx
@@ -432,9 +432,6 @@
           <t>Ouvert</t>
         </is>
       </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -452,9 +449,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -492,9 +486,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -572,9 +563,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -692,9 +680,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -732,9 +717,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -792,9 +774,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -812,9 +791,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D23">
-        <v>2</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -852,9 +828,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -912,9 +885,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -952,9 +922,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1032,9 +999,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1091,9 +1055,6 @@
         <is>
           <t>Mefiant</t>
         </is>
-      </c>
-      <c r="D37">
-        <v>1</v>
       </c>
     </row>
     <row r="38">

--- a/docs/downloads/13/tbl_synthese_qualite_alaotra_tous.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_alaotra_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -399,7 +399,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -419,7 +419,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -436,7 +436,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -490,7 +490,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -778,7 +778,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -815,7 +815,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -832,7 +832,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -909,7 +909,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -926,7 +926,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -966,7 +966,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -986,7 +986,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1023,7 +1023,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1043,7 +1043,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1080,7 +1080,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1120,7 +1120,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1140,7 +1140,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
